--- a/src/main/resources/templates/shipping-mark-template.xlsx
+++ b/src/main/resources/templates/shipping-mark-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alan.zhao/Code/Scione/projects/scione-scm-procurement/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alan.zhao/Code/Scione/projects/scione-scm-procurement/src/main/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AAEEA2-4B30-8743-97B1-1872A85C61A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5061BF-AE7A-2945-9F41-AD3883F7E546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="780" windowWidth="28800" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="780" windowWidth="28800" windowHeight="12380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="合同模板" sheetId="1" r:id="rId1"/>
@@ -203,18 +203,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -259,9 +253,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -283,13 +274,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -595,80 +589,80 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="26" customHeight="1">
-      <c r="A2" s="5"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="12" t="str">
+      <c r="C2" s="5"/>
+      <c r="D2" s="13" t="str">
         <f>_xlfn.DISPIMG("ID_EA79BAC59F5D48DDA73110FD6B8C7F42",1)</f>
         <v>=DISPIMG("ID_EA79BAC59F5D48DDA73110FD6B8C7F42",1)</v>
       </c>
-      <c r="E2" s="12"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" ht="26" customHeight="1">
-      <c r="A3" s="5"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="1:5" ht="26" customHeight="1">
-      <c r="A4" s="8"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="26" customHeight="1">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="26" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="109" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="14" t="str">
+      <c r="C7" s="12" t="str">
         <f>_xlfn.DISPIMG("ID_19C5C4A065724DC6AD4D971564D4D23F",1)</f>
         <v>=DISPIMG("ID_19C5C4A065724DC6AD4D971564D4D23F",1)</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" ht="18">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8"/>
       <c r="E8"/>
     </row>
